--- a/outputs_xlsx_solution/prog-loop.4-wide.xlsx
+++ b/outputs_xlsx_solution/prog-loop.4-wide.xlsx
@@ -77,7 +77,10 @@
     <t>fsd F0, 0(X2)</t>
   </si>
   <si>
-    <t>IS/EX</t>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>addi X1, X1, -8</t>
@@ -89,10 +92,13 @@
     <t>bne X1, X0, 12</t>
   </si>
   <si>
-    <t>WB/CT</t>
-  </si>
-  <si>
-    <t>EX</t>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>RS Stall</t>
   </si>
   <si>
     <t>[Legend]</t>
@@ -104,13 +110,31 @@
     <t>Instruction Decode</t>
   </si>
   <si>
-    <t>Add to Issue Queue/Execute (if instruction is ready, it can start executing in the same cycle it is added to issue queue)</t>
-  </si>
-  <si>
-    <t>Execute</t>
-  </si>
-  <si>
-    <t>Write Back/Commit (instruction can be committed on the same cycle it writes back)</t>
+    <t>Add to Issue Queue</t>
+  </si>
+  <si>
+    <t>Execute (instruction can execute on the same cycle as it is added to the issue queue, if it is ready)</t>
+  </si>
+  <si>
+    <t>Write Back</t>
+  </si>
+  <si>
+    <t>Commit (instruction can commit on the same cycle as write back, if at the head)</t>
+  </si>
+  <si>
+    <t>Reservation Station Stall (stalled because reservation stations are full)</t>
+  </si>
+  <si>
+    <t>ROB Stall</t>
+  </si>
+  <si>
+    <t>Reorder Buffer Stall (stalled because the ROB is full)</t>
+  </si>
+  <si>
+    <t>CDB Stall</t>
+  </si>
+  <si>
+    <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
   </si>
 </sst>
 </file>
@@ -540,6 +564,12 @@
       <c r="X1">
         <v>21</v>
       </c>
+      <c r="Y1">
+        <v>22</v>
+      </c>
+      <c r="Z1">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -561,7 +591,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -584,10 +614,10 @@
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -610,10 +640,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -633,13 +663,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -659,22 +689,22 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -694,16 +724,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -723,19 +753,19 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -755,13 +785,13 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -772,7 +802,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -784,10 +814,10 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -798,7 +828,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -810,13 +840,13 @@
         <v>14</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -827,7 +857,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -836,16 +866,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -865,16 +895,16 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>18</v>
-      </c>
-      <c r="R13" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="S13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -894,22 +924,25 @@
         <v>9</v>
       </c>
       <c r="L14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q14" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="S14" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -929,16 +962,16 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>18</v>
-      </c>
-      <c r="R15" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="S15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -958,19 +991,19 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="S16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="T16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +1023,13 @@
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1040,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -1016,16 +1049,16 @@
         <v>9</v>
       </c>
       <c r="M18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N18" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1036,7 +1069,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -1045,56 +1078,56 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>18</v>
+      </c>
+      <c r="K20" t="s">
+        <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O20" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L21" t="s">
         <v>5</v>
@@ -1103,36 +1136,27 @@
         <v>9</v>
       </c>
       <c r="N21" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" t="s">
         <v>14</v>
       </c>
       <c r="P21" t="s">
         <v>19</v>
       </c>
-      <c r="Q21" t="s">
-        <v>19</v>
-      </c>
-      <c r="R21" t="s">
-        <v>19</v>
-      </c>
-      <c r="S21" t="s">
-        <v>19</v>
-      </c>
-      <c r="T21" t="s">
-        <v>18</v>
-      </c>
-      <c r="V21" t="s">
-        <v>18</v>
+      <c r="W21" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L22" t="s">
         <v>5</v>
@@ -1140,28 +1164,37 @@
       <c r="M22" t="s">
         <v>9</v>
       </c>
-      <c r="O22" t="s">
-        <v>14</v>
-      </c>
-      <c r="P22" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>18</v>
+      <c r="N22" t="s">
+        <v>15</v>
+      </c>
+      <c r="R22" t="s">
+        <v>14</v>
+      </c>
+      <c r="S22" t="s">
+        <v>14</v>
+      </c>
+      <c r="T22" t="s">
+        <v>14</v>
+      </c>
+      <c r="U22" t="s">
+        <v>14</v>
       </c>
       <c r="V22" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="W22" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L23" t="s">
         <v>5</v>
@@ -1169,57 +1202,63 @@
       <c r="M23" t="s">
         <v>9</v>
       </c>
+      <c r="N23" t="s">
+        <v>21</v>
+      </c>
       <c r="O23" t="s">
-        <v>14</v>
-      </c>
-      <c r="T23" t="s">
-        <v>19</v>
-      </c>
-      <c r="U23" t="s">
-        <v>19</v>
-      </c>
-      <c r="V23" t="s">
+        <v>15</v>
+      </c>
+      <c r="P23" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q23" t="s">
         <v>19</v>
       </c>
       <c r="W23" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
         <v>24</v>
       </c>
-      <c r="B24">
-        <v>28</v>
-      </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="L24" t="s">
+        <v>5</v>
       </c>
       <c r="M24" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" t="s">
-        <v>9</v>
-      </c>
-      <c r="R24" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" t="s">
+        <v>15</v>
+      </c>
+      <c r="V24" t="s">
         <v>14</v>
       </c>
       <c r="W24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="X24" t="s">
-        <v>18</v>
+        <v>14</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M25" t="s">
         <v>5</v>
@@ -1227,25 +1266,31 @@
       <c r="N25" t="s">
         <v>9</v>
       </c>
+      <c r="O25" t="s">
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>21</v>
+      </c>
       <c r="R25" t="s">
-        <v>14</v>
-      </c>
-      <c r="S25" t="s">
-        <v>19</v>
-      </c>
-      <c r="T25" t="s">
-        <v>18</v>
-      </c>
-      <c r="X25" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
@@ -1257,24 +1302,24 @@
         <v>9</v>
       </c>
       <c r="R26" t="s">
+        <v>15</v>
+      </c>
+      <c r="S26" t="s">
         <v>14</v>
       </c>
       <c r="T26" t="s">
         <v>19</v>
       </c>
-      <c r="U26" t="s">
-        <v>18</v>
-      </c>
-      <c r="X26" t="s">
-        <v>18</v>
+      <c r="Z26" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
         <v>17</v>
@@ -1286,61 +1331,114 @@
         <v>9</v>
       </c>
       <c r="R27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="U27" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
         <v>18</v>
       </c>
-      <c r="X27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
+      <c r="M28" t="s">
+        <v>5</v>
+      </c>
+      <c r="N28" t="s">
+        <v>9</v>
+      </c>
+      <c r="R28" t="s">
+        <v>15</v>
+      </c>
+      <c r="T28" t="s">
+        <v>14</v>
+      </c>
+      <c r="U28" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z28" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/outputs_xlsx_solution/prog-loop.4-wide.xlsx
+++ b/outputs_xlsx_solution/prog-loop.4-wide.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>IS</t>
   </si>
   <si>
@@ -135,6 +138,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -591,7 +597,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -611,13 +617,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -640,10 +646,10 @@
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -663,13 +669,13 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
         <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -689,7 +695,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
         <v>14</v>
@@ -704,7 +710,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -724,16 +730,16 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -753,7 +759,7 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
         <v>14</v>
@@ -765,7 +771,7 @@
         <v>14</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -785,13 +791,19 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O9" t="s">
         <v>15</v>
       </c>
+      <c r="P9" t="s">
+        <v>15</v>
+      </c>
       <c r="Q9" t="s">
         <v>14</v>
       </c>
       <c r="R9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -802,7 +814,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -814,10 +826,10 @@
         <v>14</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -828,7 +840,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -837,16 +849,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I11" t="s">
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -857,7 +869,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -866,16 +878,16 @@
         <v>9</v>
       </c>
       <c r="H12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -895,16 +907,16 @@
         <v>9</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
         <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -924,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N14" t="s">
         <v>14</v>
@@ -939,10 +951,10 @@
         <v>14</v>
       </c>
       <c r="R14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -962,16 +974,19 @@
         <v>9</v>
       </c>
       <c r="L15" t="s">
+        <v>16</v>
+      </c>
+      <c r="M15" t="s">
         <v>15</v>
       </c>
       <c r="N15" t="s">
         <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -991,7 +1006,7 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R16" t="s">
         <v>14</v>
@@ -1003,7 +1018,7 @@
         <v>14</v>
       </c>
       <c r="U16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -1023,13 +1038,13 @@
         <v>9</v>
       </c>
       <c r="M17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U17" t="s">
         <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -1040,7 +1055,7 @@
         <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" t="s">
         <v>5</v>
@@ -1049,16 +1064,16 @@
         <v>9</v>
       </c>
       <c r="M18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N18" t="s">
         <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1069,7 +1084,7 @@
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K19" t="s">
         <v>5</v>
@@ -1078,16 +1093,19 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" t="s">
         <v>15</v>
       </c>
       <c r="O19" t="s">
         <v>14</v>
       </c>
       <c r="P19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1098,7 +1116,7 @@
         <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="s">
         <v>5</v>
@@ -1107,16 +1125,16 @@
         <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
         <v>14</v>
       </c>
       <c r="P20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -1136,16 +1154,16 @@
         <v>9</v>
       </c>
       <c r="N21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O21" t="s">
         <v>14</v>
       </c>
       <c r="P21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1165,8 +1183,14 @@
         <v>9</v>
       </c>
       <c r="N22" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" t="s">
         <v>15</v>
       </c>
+      <c r="Q22" t="s">
+        <v>15</v>
+      </c>
       <c r="R22" t="s">
         <v>14</v>
       </c>
@@ -1180,10 +1204,10 @@
         <v>14</v>
       </c>
       <c r="V22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -1203,19 +1227,19 @@
         <v>9</v>
       </c>
       <c r="N23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P23" t="s">
         <v>14</v>
       </c>
       <c r="Q23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1235,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="O24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V24" t="s">
         <v>14</v>
@@ -1247,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="Y24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1267,22 +1291,22 @@
         <v>9</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y25" t="s">
         <v>14</v>
       </c>
       <c r="Z25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26">
@@ -1293,7 +1317,7 @@
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M26" t="s">
         <v>5</v>
@@ -1302,16 +1326,16 @@
         <v>9</v>
       </c>
       <c r="R26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S26" t="s">
         <v>14</v>
       </c>
       <c r="T26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1322,7 +1346,7 @@
         <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M27" t="s">
         <v>5</v>
@@ -1331,16 +1355,19 @@
         <v>9</v>
       </c>
       <c r="R27" t="s">
+        <v>16</v>
+      </c>
+      <c r="S27" t="s">
         <v>15</v>
       </c>
       <c r="T27" t="s">
         <v>14</v>
       </c>
       <c r="U27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1351,7 +1378,7 @@
         <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M28" t="s">
         <v>5</v>
@@ -1360,21 +1387,21 @@
         <v>9</v>
       </c>
       <c r="R28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T28" t="s">
         <v>14</v>
       </c>
       <c r="U28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
@@ -1382,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -1390,15 +1417,15 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
@@ -1406,39 +1433,55 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" t="s">
         <v>32</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
         <v>33</v>
+      </c>
+      <c r="B39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
